--- a/data/trans_orig/P39B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023</t>
+          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282131</t>
+          <t>282402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>298758</t>
+          <t>298761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>265484</t>
+          <t>265350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>278397</t>
+          <t>278062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>553887</t>
+          <t>552904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>574948</t>
+          <t>574181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>36345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429901</t>
+          <t>431801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>462050</t>
+          <t>462243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>439018</t>
+          <t>439130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>461800</t>
+          <t>461659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>877591</t>
+          <t>881187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>917212</t>
+          <t>919592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>39683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>1254</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4161</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>268547</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>284719</t>
+          <t>284464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298975</t>
+          <t>297902</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313886</t>
+          <t>313311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>572852</t>
+          <t>572826</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>594637</t>
+          <t>595219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>291592</t>
+          <t>291884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>300075</t>
+          <t>299802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>436990</t>
+          <t>437556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>450770</t>
+          <t>450737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>733685</t>
+          <t>733421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>748653</t>
+          <t>748128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3228,97 +3228,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2674</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2945</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2776</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3458,97 +3458,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,97 +3571,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174398</t>
+          <t>174613</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>178293</t>
+          <t>178407</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>202153</t>
+          <t>202108</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>206952</t>
+          <t>206892</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>378813</t>
+          <t>378747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>384652</t>
+          <t>384643</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>487</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>206706</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>227832</t>
+          <t>228011</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>216387</t>
+          <t>216185</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>414415</t>
+          <t>414461</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>440542</t>
+          <t>439919</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>44303</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>587751</t>
+          <t>586991</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>603327</t>
+          <t>602816</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>799158</t>
+          <t>797752</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>828347</t>
+          <t>828754</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1410663</t>
+          <t>1410664</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1395011</t>
+          <t>1394753</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1427034</t>
+          <t>1426244</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17419</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1451620</t>
+          <t>1451621</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1451620</t>
+          <t>1451621</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1451620</t>
+          <t>1451621</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5504,82 +5504,82 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4091</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>849896</t>
+          <t>849562</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>909308</t>
+          <t>906581</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>667289</t>
+          <t>668624</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>686056</t>
+          <t>687108</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1527476</t>
+          <t>1525806</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1595307</t>
+          <t>1589495</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>53917</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33644</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>34142</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>78713</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>43238</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>83598</t>
+          <t>83456</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3148228</t>
+          <t>3149617</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3230814</t>
+          <t>3231408</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3352878</t>
+          <t>3355173</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3420231</t>
+          <t>3420313</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6522834</t>
+          <t>6518804</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6623232</t>
+          <t>6621175</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>120525</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>110088</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>159994</t>
+          <t>160287</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>216101</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Provincia-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>292039</t>
+          <t>291418</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282402</t>
+          <t>278864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>298761</t>
+          <t>299935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>273019</t>
+          <t>293955</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>265350</t>
+          <t>282749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>300334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565057</t>
+          <t>585373</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>552904</t>
+          <t>570831</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>574181</t>
+          <t>597350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>32542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>43773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25134</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>448737</t>
+          <t>458305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431801</t>
+          <t>440514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>462243</t>
+          <t>471168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>452336</t>
+          <t>479866</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>439130</t>
+          <t>467193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>461659</t>
+          <t>489345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>901073</t>
+          <t>938171</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>881187</t>
+          <t>917214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>919592</t>
+          <t>956096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>27493</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>497022</t>
+          <t>508989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>497022</t>
+          <t>508989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>497022</t>
+          <t>508989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>487427</t>
+          <t>516488</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>487427</t>
+          <t>516488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>487427</t>
+          <t>516488</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>984449</t>
+          <t>1025477</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>984449</t>
+          <t>1025477</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>984449</t>
+          <t>1025477</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>277694</t>
+          <t>276535</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267599</t>
+          <t>267618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>284464</t>
+          <t>284908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>306798</t>
+          <t>311399</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>297902</t>
+          <t>302040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313311</t>
+          <t>318830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>584492</t>
+          <t>587933</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>572826</t>
+          <t>575737</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>595219</t>
+          <t>598471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,22 +2463,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>16645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,22 +2611,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>302305</t>
+          <t>300831</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>302305</t>
+          <t>300831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>302305</t>
+          <t>300831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>332312</t>
+          <t>339091</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>332312</t>
+          <t>339091</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>332312</t>
+          <t>339091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>634616</t>
+          <t>639922</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>634616</t>
+          <t>639922</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>634616</t>
+          <t>639922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>297269</t>
+          <t>349347</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>291884</t>
+          <t>342342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>299802</t>
+          <t>352516</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>445145</t>
+          <t>386316</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>437556</t>
+          <t>378821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>450737</t>
+          <t>390902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>742412</t>
+          <t>735662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>733421</t>
+          <t>726014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>748128</t>
+          <t>741795</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>854</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>854</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>301071</t>
+          <t>354262</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>301071</t>
+          <t>354262</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>301071</t>
+          <t>354262</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>455806</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>455806</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>455806</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>756876</t>
+          <t>751898</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>756876</t>
+          <t>751898</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>756876</t>
+          <t>751898</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3679,69 +3679,69 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>177267</t>
+          <t>201445</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174613</t>
+          <t>193476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>178407</t>
+          <t>204389</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>222834</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>219411</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>224940</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>205196</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>202108</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>206892</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>757</t>
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>382463</t>
+          <t>424279</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>378747</t>
+          <t>416902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>384643</t>
+          <t>427936</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>779</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>799</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>218365</t>
+          <t>218359</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>206706</t>
+          <t>207462</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>228011</t>
+          <t>227670</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>209765</t>
+          <t>213608</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>201857</t>
+          <t>204304</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>220391</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>428130</t>
+          <t>431967</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>414461</t>
+          <t>418672</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>439919</t>
+          <t>443041</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -4474,22 +4474,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33547</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44303</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>19030</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>25975</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>258801</t>
+          <t>257945</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>258801</t>
+          <t>257945</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>258801</t>
+          <t>257945</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>238381</t>
+          <t>244224</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>238381</t>
+          <t>244224</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>238381</t>
+          <t>244224</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>497182</t>
+          <t>502168</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>497182</t>
+          <t>502168</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>497182</t>
+          <t>502168</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>597016</t>
+          <t>688791</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>586991</t>
+          <t>679010</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>602816</t>
+          <t>695450</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>813649</t>
+          <t>725363</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>797752</t>
+          <t>711725</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>828754</t>
+          <t>735333</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1410664</t>
+          <t>1414156</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1394753</t>
+          <t>1398924</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5269,22 +5269,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>611014</t>
+          <t>705296</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>611014</t>
+          <t>705296</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>611014</t>
+          <t>705296</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>840607</t>
+          <t>759328</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>840607</t>
+          <t>759328</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>840607</t>
+          <t>759328</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1451621</t>
+          <t>1464625</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1451621</t>
+          <t>1464625</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1451621</t>
+          <t>1464625</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,67 +5647,67 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>11211</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>3867</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>9893</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>875229</t>
+          <t>723547</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>849562</t>
+          <t>700189</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>906581</t>
+          <t>738935</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>677335</t>
+          <t>779139</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>668624</t>
+          <t>765801</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>687108</t>
+          <t>790035</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1552565</t>
+          <t>1502686</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1525806</t>
+          <t>1475480</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1589495</t>
+          <t>1522420</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>54084</t>
+          <t>65186</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>19296</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>61032</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>64909</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>80225</t>
+          <t>99078</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>40315</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>56230</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,27 +6181,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>82903</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6294,67 +6294,67 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>41482</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>32187</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>56904</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>33177</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>23582</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>43238</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>48644</t>
+          <t>58901</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>83456</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3183614</t>
+          <t>3207747</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3149617</t>
+          <t>3174851</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3231408</t>
+          <t>3237412</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3383242</t>
+          <t>3412483</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3355173</t>
+          <t>3385023</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3420313</t>
+          <t>3436917</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>6566857</t>
+          <t>6620229</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6518804</t>
+          <t>6571021</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6621175</t>
+          <t>6656425</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>121619</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>144890</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>90573</t>
+          <t>103357</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>71929</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>122365</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>224976</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>160287</t>
+          <t>199243</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>218099</t>
+          <t>256491</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>44012</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>63588</t>
+          <t>75820</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>78463</t>
+          <t>93588</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>99425</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
